--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -132,9 +132,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:X59" headerRowCount="1">
-  <autoFilter ref="A1:X59"/>
-  <tableColumns count="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:AA59" headerRowCount="1">
+  <autoFilter ref="A1:AA59"/>
+  <tableColumns count="27">
     <tableColumn id="1" name="工程名"/>
     <tableColumn id="2" name="機械名"/>
     <tableColumn id="3" name="受注日"/>
@@ -159,6 +159,9 @@
     <tableColumn id="22" name="原反投入場所"/>
     <tableColumn id="23" name="配台日"/>
     <tableColumn id="24" name="当日配台数量"/>
+    <tableColumn id="25" name="__受注日_norm"/>
+    <tableColumn id="26" name="__工程名_norm"/>
+    <tableColumn id="27" name="__依頼NO_norm"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:AA59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,6 +580,21 @@
           <t>当日配台数量</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>__受注日_norm</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>__工程名_norm</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>__依頼NO_norm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -651,6 +669,17 @@
       <c r="X2" t="n">
         <v>300</v>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>巻返し</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>A5-1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -725,6 +754,17 @@
       <c r="X3" t="n">
         <v>1200</v>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>A5-2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -799,6 +839,17 @@
       <c r="X4" t="n">
         <v>2100</v>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>A5-2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -871,6 +922,17 @@
       <c r="X5" t="n">
         <v>300</v>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>JR260501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -943,6 +1005,17 @@
       <c r="X6" t="n">
         <v>300</v>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>スリット</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>JR260501</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1090,17 @@
       <c r="X7" t="n">
         <v>2300</v>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>PN04-03</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1091,6 +1175,17 @@
       <c r="X8" t="n">
         <v>4200</v>
       </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>スリット</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>S260420-1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1165,6 +1260,17 @@
       <c r="X9" t="n">
         <v>1800</v>
       </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>スリット</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>S260420-1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1237,6 +1343,17 @@
       <c r="X10" t="n">
         <v>5600</v>
       </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>V5-1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1309,6 +1426,17 @@
       <c r="X11" t="n">
         <v>3000</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>V5-1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1381,6 +1509,17 @@
       <c r="X12" t="n">
         <v>2000</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>V5-2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1453,6 +1592,17 @@
       <c r="X13" t="n">
         <v>300</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>V5-3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1527,6 +1677,17 @@
       <c r="X14" t="n">
         <v>3000</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>W4-11</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1601,6 +1762,17 @@
       <c r="X15" t="n">
         <v>3300</v>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>W4-12</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1675,6 +1847,17 @@
       <c r="X16" t="n">
         <v>2400</v>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>W4-12</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1747,6 +1930,17 @@
       <c r="X17" t="n">
         <v>1500</v>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>W5-1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1819,6 +2013,17 @@
       <c r="X18" t="n">
         <v>1500</v>
       </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>巻返し</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>W5-1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1891,6 +2096,17 @@
       <c r="X19" t="n">
         <v>4200</v>
       </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1963,6 +2179,17 @@
       <c r="X20" t="n">
         <v>1800</v>
       </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2035,6 +2262,17 @@
       <c r="X21" t="n">
         <v>600</v>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2107,6 +2345,17 @@
       <c r="X22" t="n">
         <v>3300</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2179,6 +2428,17 @@
       <c r="X23" t="n">
         <v>2100</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2251,6 +2511,17 @@
       <c r="X24" t="n">
         <v>1500</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>W5-3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2323,6 +2594,17 @@
       <c r="X25" t="n">
         <v>4500</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>W5-3</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2395,6 +2677,17 @@
       <c r="X26" t="n">
         <v>1200</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>W5-3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2467,6 +2760,17 @@
       <c r="X27" t="n">
         <v>3300</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>W5-3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2539,6 +2843,17 @@
       <c r="X28" t="n">
         <v>1500</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>W5-3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2611,6 +2926,17 @@
       <c r="X29" t="n">
         <v>4200</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>W5-4</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2683,6 +3009,17 @@
       <c r="X30" t="n">
         <v>4800</v>
       </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>W5-4</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2755,6 +3092,17 @@
       <c r="X31" t="n">
         <v>1500</v>
       </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>W5-4</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2827,6 +3175,17 @@
       <c r="X32" t="n">
         <v>3300</v>
       </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>W5-4</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2899,6 +3258,17 @@
       <c r="X33" t="n">
         <v>3300</v>
       </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>W5-4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2971,6 +3341,17 @@
       <c r="X34" t="n">
         <v>900</v>
       </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>W5-4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3045,6 +3426,17 @@
       <c r="X35" t="n">
         <v>1000</v>
       </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Y4-49</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3119,6 +3511,17 @@
       <c r="X36" t="n">
         <v>1000</v>
       </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Y4-50</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3193,6 +3596,17 @@
       <c r="X37" t="n">
         <v>1000</v>
       </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Y4-50</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3267,6 +3681,17 @@
       <c r="X38" t="n">
         <v>1000</v>
       </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Y4-51</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3341,6 +3766,17 @@
       <c r="X39" t="n">
         <v>1000</v>
       </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>スリット</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Y4-51</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3415,6 +3851,17 @@
       <c r="X40" t="n">
         <v>2200</v>
       </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Y4-52</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3489,6 +3936,17 @@
       <c r="X41" t="n">
         <v>1000</v>
       </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Y4-53</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3563,6 +4021,17 @@
       <c r="X42" t="n">
         <v>600</v>
       </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Y4-54</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3637,6 +4106,17 @@
       <c r="X43" t="n">
         <v>600</v>
       </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Y4-54</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3709,6 +4189,17 @@
       <c r="X44" t="n">
         <v>400</v>
       </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>分割</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Y4-58</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3781,6 +4272,17 @@
       <c r="X45" t="n">
         <v>5100</v>
       </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Y4-59</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3853,6 +4355,17 @@
       <c r="X46" t="n">
         <v>2400</v>
       </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Y4-59</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3927,6 +4440,17 @@
       <c r="X47" t="n">
         <v>7200</v>
       </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Y4-7</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3999,6 +4523,17 @@
       <c r="X48" t="n">
         <v>3600</v>
       </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Y5-1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4071,6 +4606,17 @@
       <c r="X49" t="n">
         <v>600</v>
       </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Y5-1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4143,6 +4689,17 @@
       <c r="X50" t="n">
         <v>4800</v>
       </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Y5-1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4215,6 +4772,17 @@
       <c r="X51" t="n">
         <v>3300</v>
       </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Y5-2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4287,6 +4855,17 @@
       <c r="X52" t="n">
         <v>5700</v>
       </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Y5-2</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4359,6 +4938,17 @@
       <c r="X53" t="n">
         <v>2400</v>
       </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Y5-3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4431,6 +5021,17 @@
       <c r="X54" t="n">
         <v>2400</v>
       </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Y5-3</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4503,6 +5104,17 @@
       <c r="X55" t="n">
         <v>200</v>
       </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Y5-4</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4575,6 +5187,17 @@
       <c r="X56" t="n">
         <v>200</v>
       </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Y5-4</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4647,6 +5270,17 @@
       <c r="X57" t="n">
         <v>1200</v>
       </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Y5-5</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4719,6 +5353,17 @@
       <c r="X58" t="n">
         <v>2000</v>
       </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Y5-6</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4790,6 +5435,17 @@
       </c>
       <c r="X59" t="n">
         <v>2000</v>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>スリット</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Y5-6</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -607,21 +607,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>78968</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>A5-1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>30060-AG00-1000X100F-A   X</t>
@@ -652,7 +666,9 @@
       <c r="Q2" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" s="1" t="n">
+        <v>46143</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -661,15 +677,25 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
       <c r="W2" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X2" t="n">
         <v>300</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>巻返し</t>
@@ -692,21 +718,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D3" t="n">
+        <v>79090</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>A5-2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>40050-BG00-1080X210F-A   X</t>
@@ -737,7 +777,9 @@
       <c r="Q3" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" s="1" t="n">
+        <v>46149</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -746,15 +788,25 @@
       <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W3" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X3" t="n">
         <v>1200</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -777,21 +829,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D4" t="n">
+        <v>79090</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>A5-2</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>40050-BG00-1080X210F-A   X</t>
@@ -822,7 +888,9 @@
       <c r="Q4" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" s="1" t="n">
+        <v>46150</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -831,15 +899,25 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W4" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X4" t="n">
         <v>2100</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>接続</t>
@@ -862,21 +940,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D5" t="n">
+        <v>79063</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>JR260501</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7A1 </t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0   </t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">40040-E10W- 870X 95   </t>
@@ -905,7 +997,9 @@
         <v>46150</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" s="1" t="n">
+        <v>46143</v>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -914,15 +1008,25 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>300</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W5" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="X5" t="n">
         <v>300</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -945,21 +1049,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D6" t="n">
+        <v>79063</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>JR260501</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7A1 </t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0   </t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">40040-E10W- 870X 95   </t>
@@ -988,7 +1106,9 @@
         <v>46150</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -997,15 +1117,25 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>300</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W6" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="X6" t="n">
         <v>300</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>スリット</t>
@@ -1028,21 +1158,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="D7" t="n">
+        <v>78887</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>PN04-03</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7A1 </t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7C8 </t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>FEL3002BY05WDLG-EC</t>
@@ -1073,7 +1217,9 @@
       <c r="Q7" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" s="1" t="n">
+        <v>46140</v>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1082,15 +1228,25 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W7" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="X7" t="n">
         <v>2300</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026/04/16</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>EC</t>
@@ -1113,21 +1269,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D8" t="n">
+        <v>78976</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>S260420-1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 535X200F-AGA1C</t>
@@ -1137,7 +1307,7 @@
         <v>6000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1158,24 +1328,36 @@
       <c r="Q8" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>0:未完</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
       <c r="W8" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X8" t="n">
         <v>4200</v>
       </c>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>スリット</t>
@@ -1198,21 +1380,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D9" t="n">
+        <v>78976</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>S260420-1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 535X200F-AGA1C</t>
@@ -1222,7 +1418,7 @@
         <v>6000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1243,24 +1439,36 @@
       <c r="Q9" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>0:未完</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
       <c r="W9" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="X9" t="n">
         <v>1800</v>
       </c>
-      <c r="Y9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>スリット</t>
@@ -1283,21 +1491,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79141</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>V5-1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>8600</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>30060-AG00-1000X100F-A   C</t>
@@ -1326,7 +1548,9 @@
         <v>46157</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1335,15 +1559,25 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>8600</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
       <c r="W10" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X10" t="n">
         <v>5600</v>
       </c>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>分割</t>
@@ -1366,21 +1600,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D11" t="n">
+        <v>79141</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>V5-1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>8600</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>30060-AG00-1000X100F-A   C</t>
@@ -1409,7 +1657,9 @@
         <v>46157</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1418,15 +1668,25 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>8600</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
       <c r="W11" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X11" t="n">
         <v>3000</v>
       </c>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>分割</t>
@@ -1449,21 +1709,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D12" t="n">
+        <v>79142</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>V5-2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>30030-BG00-1000X100F-A   C</t>
@@ -1492,7 +1766,9 @@
         <v>46157</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1501,15 +1777,25 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W12" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X12" t="n">
         <v>2000</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -1532,21 +1818,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D13" t="n">
+        <v>79143</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>V5-3</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>30060-AG00-1000X100F-ABK0C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>30030-BG00-1000X100F-ABK0C</t>
@@ -1575,7 +1875,9 @@
         <v>46156</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1584,15 +1886,25 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>300</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W13" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X13" t="n">
         <v>300</v>
       </c>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -1615,21 +1927,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="C14" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="D14" t="n">
+        <v>78623</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>W4-11</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -1639,7 +1965,7 @@
         <v>6000</v>
       </c>
       <c r="L14" t="n">
-        <v>3000</v>
+        <v>5400</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1660,24 +1986,36 @@
       <c r="Q14" s="1" t="n">
         <v>46140</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>0:未完</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>2400</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+        <v>5400</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W14" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X14" t="n">
         <v>3000</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>検査</t>
@@ -1700,21 +2038,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="C15" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="D15" t="n">
+        <v>78624</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>W4-12</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -1745,7 +2097,9 @@
       <c r="Q15" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" s="1" t="n">
+        <v>46141</v>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1754,15 +2108,25 @@
       <c r="T15" t="n">
         <v>0</v>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>5700</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="X15" t="n">
         <v>3300</v>
       </c>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>検査</t>
@@ -1785,21 +2149,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="C16" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="D16" t="n">
+        <v>78624</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>W4-12</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -1830,7 +2208,9 @@
       <c r="Q16" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" s="1" t="n">
+        <v>46141</v>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1839,15 +2219,25 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>5700</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W16" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="X16" t="n">
         <v>2400</v>
       </c>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>検査</t>
@@ -1870,21 +2260,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="C17" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D17" t="n">
+        <v>79067</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>W5-1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>15025-JH1F-1550X250F-A   S</t>
@@ -1913,7 +2317,9 @@
         <v>46155</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" s="1" t="n">
+        <v>46150</v>
+      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -1922,15 +2328,25 @@
       <c r="T17" t="n">
         <v>0</v>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>1250</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W17" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="X17" t="n">
         <v>1500</v>
       </c>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>EC</t>
@@ -1953,21 +2369,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D18" t="n">
+        <v>79067</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>W5-1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>15025-JH1F-1550X250F-A   S</t>
@@ -1996,7 +2426,9 @@
         <v>46155</v>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" s="1" t="n">
+        <v>46150</v>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2005,15 +2437,25 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X18" t="n">
         <v>1500</v>
       </c>
-      <c r="Y18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>巻返し</t>
@@ -2036,21 +2478,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="C19" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D19" t="n">
+        <v>79138</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>W5-2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2079,7 +2535,9 @@
         <v>46156</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2088,15 +2546,25 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X19" t="n">
         <v>4200</v>
       </c>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>EC</t>
@@ -2119,21 +2587,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="C20" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D20" t="n">
+        <v>79138</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>W5-2</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2162,7 +2644,9 @@
         <v>46156</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2171,15 +2655,25 @@
       <c r="T20" t="n">
         <v>0</v>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W20" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X20" t="n">
         <v>1800</v>
       </c>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
           <t>EC</t>
@@ -2202,21 +2696,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="C21" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D21" t="n">
+        <v>79138</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>W5-2</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2245,7 +2753,9 @@
         <v>46156</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2254,15 +2764,25 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W21" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X21" t="n">
         <v>600</v>
       </c>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>検査</t>
@@ -2285,21 +2805,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="C22" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D22" t="n">
+        <v>79138</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>W5-2</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2328,7 +2862,9 @@
         <v>46156</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2337,15 +2873,25 @@
       <c r="T22" t="n">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W22" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="X22" t="n">
         <v>3300</v>
       </c>
-      <c r="Y22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
           <t>検査</t>
@@ -2368,21 +2914,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D23" t="n">
+        <v>79138</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>W5-2</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2411,7 +2971,9 @@
         <v>46156</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2420,15 +2982,25 @@
       <c r="T23" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W23" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="X23" t="n">
         <v>2100</v>
       </c>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
           <t>検査</t>
@@ -2451,21 +3023,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D24" t="n">
+        <v>79139</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>W5-3</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2494,7 +3080,9 @@
         <v>46162</v>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2503,15 +3091,25 @@
       <c r="T24" t="n">
         <v>0</v>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W24" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X24" t="n">
         <v>1500</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>EC</t>
@@ -2534,21 +3132,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="C25" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D25" t="n">
+        <v>79139</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>W5-3</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2577,7 +3189,9 @@
         <v>46162</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2586,15 +3200,25 @@
       <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W25" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="X25" t="n">
         <v>4500</v>
       </c>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
           <t>EC</t>
@@ -2617,21 +3241,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D26" t="n">
+        <v>79139</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>W5-3</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2660,7 +3298,9 @@
         <v>46162</v>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2669,15 +3309,25 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W26" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="X26" t="n">
         <v>1200</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
           <t>検査</t>
@@ -2700,21 +3350,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="C27" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D27" t="n">
+        <v>79139</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>W5-3</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2743,7 +3407,9 @@
         <v>46162</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2752,15 +3418,25 @@
       <c r="T27" t="n">
         <v>0</v>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W27" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="X27" t="n">
         <v>3300</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
           <t>検査</t>
@@ -2783,21 +3459,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D28" t="n">
+        <v>79139</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>W5-3</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>15020-JX5R-1300X300F-A   R</t>
@@ -2826,7 +3516,9 @@
         <v>46162</v>
       </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2835,15 +3527,25 @@
       <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W28" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="X28" t="n">
         <v>1500</v>
       </c>
-      <c r="Y28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>検査</t>
@@ -2866,21 +3568,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="C29" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D29" t="n">
+        <v>79140</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>W5-4</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -2909,7 +3625,9 @@
         <v>46154</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -2918,15 +3636,25 @@
       <c r="T29" t="n">
         <v>0</v>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W29" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="X29" t="n">
         <v>4200</v>
       </c>
-      <c r="Y29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>EC</t>
@@ -2949,21 +3677,35 @@
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D30" t="n">
+        <v>79140</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>W5-4</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -2992,7 +3734,9 @@
         <v>46154</v>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3001,15 +3745,25 @@
       <c r="T30" t="n">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W30" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="X30" t="n">
         <v>4800</v>
       </c>
-      <c r="Y30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>EC</t>
@@ -3032,21 +3786,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="C31" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D31" t="n">
+        <v>79140</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>W5-4</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -3075,7 +3843,9 @@
         <v>46154</v>
       </c>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3084,15 +3854,25 @@
       <c r="T31" t="n">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="X31" t="n">
         <v>1500</v>
       </c>
-      <c r="Y31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr">
         <is>
           <t>検査</t>
@@ -3115,21 +3895,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="C32" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D32" t="n">
+        <v>79140</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>W5-4</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -3158,7 +3952,9 @@
         <v>46154</v>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3167,15 +3963,25 @@
       <c r="T32" t="n">
         <v>0</v>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="X32" t="n">
         <v>3300</v>
       </c>
-      <c r="Y32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
           <t>検査</t>
@@ -3198,21 +4004,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="C33" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D33" t="n">
+        <v>79140</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>W5-4</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -3241,7 +4061,9 @@
         <v>46154</v>
       </c>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3250,15 +4072,25 @@
       <c r="T33" t="n">
         <v>0</v>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W33" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X33" t="n">
         <v>3300</v>
       </c>
-      <c r="Y33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr">
         <is>
           <t>検査</t>
@@ -3281,21 +4113,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="C34" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D34" t="n">
+        <v>79140</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>W5-4</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>15020-JX5R-1440X300F-A   R</t>
@@ -3324,7 +4170,9 @@
         <v>46154</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3333,15 +4181,25 @@
       <c r="T34" t="n">
         <v>0</v>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
       <c r="W34" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X34" t="n">
         <v>900</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>検査</t>
@@ -3364,21 +4222,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="C35" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D35" t="n">
+        <v>78822</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Y4-49</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 870X200F-ABG1C</t>
@@ -3409,7 +4281,9 @@
       <c r="Q35" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3418,15 +4292,25 @@
       <c r="T35" t="n">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W35" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
       </c>
-      <c r="Y35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z35" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -3449,21 +4333,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="C36" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D36" t="n">
+        <v>78823</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Y4-50</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 870X200F-ABG1C</t>
@@ -3494,7 +4392,9 @@
       <c r="Q36" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3503,15 +4403,25 @@
       <c r="T36" t="n">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W36" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
       </c>
-      <c r="Y36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -3534,21 +4444,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="C37" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D37" t="n">
+        <v>78823</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Y4-50</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 870X200F-ABG1C</t>
@@ -3579,7 +4503,9 @@
       <c r="Q37" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S37" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3588,15 +4514,25 @@
       <c r="T37" t="n">
         <v>0</v>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W37" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
       </c>
-      <c r="Y37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z37" t="inlineStr">
         <is>
           <t>接続</t>
@@ -3619,21 +4555,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="C38" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D38" t="n">
+        <v>78826</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Y4-51</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 820X200F-A   C</t>
@@ -3664,7 +4614,9 @@
       <c r="Q38" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3673,7 +4625,9 @@
       <c r="T38" t="n">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>1000</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>46140</v>
@@ -3681,7 +4635,11 @@
       <c r="X38" t="n">
         <v>1000</v>
       </c>
-      <c r="Y38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z38" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -3704,21 +4662,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="C39" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D39" t="n">
+        <v>78826</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Y4-51</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 820X200F-A   C</t>
@@ -3728,7 +4700,7 @@
         <v>1000</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3749,16 +4721,20 @@
       <c r="Q39" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" s="1" t="n">
+        <v>46136</v>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1000</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>46140</v>
@@ -3766,7 +4742,11 @@
       <c r="X39" t="n">
         <v>1000</v>
       </c>
-      <c r="Y39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
           <t>スリット</t>
@@ -3789,21 +4769,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="C40" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D40" t="n">
+        <v>78827</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Y4-52</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 870X200F-A   C</t>
@@ -3834,7 +4828,9 @@
       <c r="Q40" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3843,15 +4839,25 @@
       <c r="T40" t="n">
         <v>0</v>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>2200</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X40" t="n">
         <v>2200</v>
       </c>
-      <c r="Y40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -3874,21 +4880,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="C41" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D41" t="n">
+        <v>78828</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Y4-53</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-ABG1C</t>
@@ -3919,7 +4939,9 @@
       <c r="Q41" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -3928,15 +4950,25 @@
       <c r="T41" t="n">
         <v>0</v>
       </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W41" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
       </c>
-      <c r="Y41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -3959,21 +4991,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="C42" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D42" t="n">
+        <v>78846</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Y4-54</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>600</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-ABG1C</t>
@@ -4004,7 +5050,9 @@
       <c r="Q42" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4013,15 +5061,25 @@
       <c r="T42" t="n">
         <v>0</v>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v>600</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W42" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="X42" t="n">
         <v>600</v>
       </c>
-      <c r="Y42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -4044,21 +5102,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D43" t="n">
+        <v>78846</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Y4-54</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>600</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-ABG1C</t>
@@ -4089,7 +5161,9 @@
       <c r="Q43" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4098,15 +5172,25 @@
       <c r="T43" t="n">
         <v>0</v>
       </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v>600</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W43" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="X43" t="n">
         <v>600</v>
       </c>
-      <c r="Y43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>接続</t>
@@ -4129,21 +5213,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="C44" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D44" t="n">
+        <v>79018</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>Y4-58</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>400</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>25020-AG00- 750X200F-AGR0C</t>
@@ -4172,7 +5270,9 @@
         <v>46149</v>
       </c>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+      <c r="R44" s="1" t="n">
+        <v>46143</v>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4181,15 +5281,25 @@
       <c r="T44" t="n">
         <v>0</v>
       </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>400</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
       <c r="W44" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="X44" t="n">
         <v>400</v>
       </c>
-      <c r="Y44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026/04/21</t>
+        </is>
+      </c>
       <c r="Z44" t="inlineStr">
         <is>
           <t>分割</t>
@@ -4212,21 +5322,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D45" t="n">
+        <v>79019</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>Y4-59</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4255,7 +5379,9 @@
         <v>46150</v>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" s="1" t="n">
+        <v>46143</v>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4264,15 +5390,25 @@
       <c r="T45" t="n">
         <v>0</v>
       </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>7500</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W45" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="X45" t="n">
         <v>5100</v>
       </c>
-      <c r="Y45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026/04/21</t>
+        </is>
+      </c>
       <c r="Z45" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4295,21 +5431,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D46" t="n">
+        <v>79019</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>Y4-59</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4338,7 +5488,9 @@
         <v>46150</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" s="1" t="n">
+        <v>46143</v>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4347,15 +5499,25 @@
       <c r="T46" t="n">
         <v>0</v>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>7500</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W46" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="X46" t="n">
         <v>2400</v>
       </c>
-      <c r="Y46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026/04/21</t>
+        </is>
+      </c>
       <c r="Z46" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4378,21 +5540,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="D47" t="n">
+        <v>78074</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Y4-7</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>9400</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>30033-BY00- 640X200F-AGA0C</t>
@@ -4402,7 +5578,7 @@
         <v>9400</v>
       </c>
       <c r="L47" t="n">
-        <v>2200</v>
+        <v>6400</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4423,24 +5599,36 @@
       <c r="Q47" s="1" t="n">
         <v>46140</v>
       </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>0:未完</t>
         </is>
       </c>
       <c r="T47" t="n">
-        <v>2400</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+        <v>12800</v>
+      </c>
+      <c r="U47" t="n">
+        <v>9400</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W47" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X47" t="n">
         <v>7200</v>
       </c>
-      <c r="Y47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026/03/25</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4463,21 +5651,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="C48" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D48" t="n">
+        <v>79070</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Y5-1</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4506,7 +5708,9 @@
         <v>46154</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4515,15 +5719,25 @@
       <c r="T48" t="n">
         <v>0</v>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W48" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="X48" t="n">
         <v>3600</v>
       </c>
-      <c r="Y48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z48" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4546,21 +5760,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="C49" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D49" t="n">
+        <v>79070</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Y5-1</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4589,7 +5817,9 @@
         <v>46154</v>
       </c>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="R49" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4598,15 +5828,25 @@
       <c r="T49" t="n">
         <v>0</v>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="X49" t="n">
         <v>600</v>
       </c>
-      <c r="Y49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z49" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4629,21 +5869,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="C50" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D50" t="n">
+        <v>79070</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Y5-1</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4672,7 +5926,9 @@
         <v>46154</v>
       </c>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4681,15 +5937,25 @@
       <c r="T50" t="n">
         <v>0</v>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W50" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X50" t="n">
         <v>4800</v>
       </c>
-      <c r="Y50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z50" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4712,21 +5978,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D51" t="n">
+        <v>79071</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Y5-2</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4755,7 +6035,9 @@
         <v>46155</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4764,15 +6046,25 @@
       <c r="T51" t="n">
         <v>0</v>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="X51" t="n">
         <v>3300</v>
       </c>
-      <c r="Y51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z51" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4795,21 +6087,35 @@
           <t>スライス機1　湖南</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="C52" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D52" t="n">
+        <v>79071</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Y5-2</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>30020-BG00- 780X300F-A   V</t>
@@ -4838,7 +6144,9 @@
         <v>46155</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4847,15 +6155,25 @@
       <c r="T52" t="n">
         <v>0</v>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X52" t="n">
         <v>5700</v>
       </c>
-      <c r="Y52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z52" t="inlineStr">
         <is>
           <t>スライス</t>
@@ -4878,21 +6196,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="C53" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D53" t="n">
+        <v>79072</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Y5-3</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>2299</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 870X200F-A   C</t>
@@ -4921,7 +6253,9 @@
         <v>46155</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" s="1" t="n">
+        <v>46153</v>
+      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -4930,15 +6264,25 @@
       <c r="T53" t="n">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" t="n">
+        <v>2299</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X53" t="n">
         <v>2400</v>
       </c>
-      <c r="Y53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z53" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -4961,21 +6305,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="C54" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D54" t="n">
+        <v>79072</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>Y5-3</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>2299</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 870X200F-A   C</t>
@@ -5004,7 +6362,9 @@
         <v>46155</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" s="1" t="n">
+        <v>46150</v>
+      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -5013,15 +6373,25 @@
       <c r="T54" t="n">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="U54" t="n">
+        <v>2299</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X54" t="n">
         <v>2400</v>
       </c>
-      <c r="Y54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z54" t="inlineStr">
         <is>
           <t>接続</t>
@@ -5044,21 +6414,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D55" t="n">
+        <v>79075</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>Y5-4</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>200</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-AGA1C</t>
@@ -5087,7 +6471,9 @@
         <v>46154</v>
       </c>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" s="1" t="n">
+        <v>46153</v>
+      </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -5096,15 +6482,25 @@
       <c r="T55" t="n">
         <v>0</v>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" t="n">
+        <v>200</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X55" t="n">
         <v>200</v>
       </c>
-      <c r="Y55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z55" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -5127,21 +6523,35 @@
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="C56" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D56" t="n">
+        <v>79075</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Y5-4</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>200</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-AGA1C</t>
@@ -5170,7 +6580,9 @@
         <v>46154</v>
       </c>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" s="1" t="n">
+        <v>46150</v>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -5179,15 +6591,25 @@
       <c r="T56" t="n">
         <v>0</v>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+      <c r="U56" t="n">
+        <v>200</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W56" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X56" t="n">
         <v>200</v>
       </c>
-      <c r="Y56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z56" t="inlineStr">
         <is>
           <t>接続</t>
@@ -5210,21 +6632,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="C57" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D57" t="n">
+        <v>79076</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Y5-5</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 680X200F-AGA1C</t>
@@ -5253,7 +6689,9 @@
         <v>46154</v>
       </c>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" s="1" t="n">
+        <v>46153</v>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -5262,15 +6700,25 @@
       <c r="T57" t="n">
         <v>0</v>
       </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="U57" t="n">
+        <v>1200</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W57" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="X57" t="n">
         <v>1200</v>
       </c>
-      <c r="Y57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z57" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -5293,21 +6741,35 @@
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="C58" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D58" t="n">
+        <v>79077</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Y5-6</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 820X200F-A   C</t>
@@ -5336,7 +6798,9 @@
         <v>46154</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" s="1" t="n">
+        <v>46153</v>
+      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -5345,15 +6809,25 @@
       <c r="T58" t="n">
         <v>0</v>
       </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="U58" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W58" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="X58" t="n">
         <v>2000</v>
       </c>
-      <c r="Y58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z58" t="inlineStr">
         <is>
           <t>SEC</t>
@@ -5376,21 +6850,35 @@
           <t>スリット機1　湖南</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="C59" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D59" t="n">
+        <v>79077</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Y5-6</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>0R040-8Y0B- 820X200F-A   C</t>
@@ -5419,7 +6907,9 @@
         <v>46154</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" s="1" t="n">
+        <v>46150</v>
+      </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>0:未完</t>
@@ -5428,15 +6918,25 @@
       <c r="T59" t="n">
         <v>0</v>
       </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="X59" t="n">
         <v>2000</v>
       </c>
-      <c r="Y59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
       <c r="Z59" t="inlineStr">
         <is>
           <t>スリット</t>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -132,9 +132,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:AA59" headerRowCount="1">
-  <autoFilter ref="A1:AA59"/>
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:X60" headerRowCount="1">
+  <autoFilter ref="A1:X60"/>
+  <tableColumns count="24">
     <tableColumn id="1" name="工程名"/>
     <tableColumn id="2" name="機械名"/>
     <tableColumn id="3" name="受注日"/>
@@ -159,9 +159,6 @@
     <tableColumn id="22" name="原反投入場所"/>
     <tableColumn id="23" name="配台日"/>
     <tableColumn id="24" name="当日配台数量"/>
-    <tableColumn id="25" name="__受注日_norm"/>
-    <tableColumn id="26" name="__工程名_norm"/>
-    <tableColumn id="27" name="__依頼NO_norm"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA59"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,21 +577,6 @@
           <t>当日配台数量</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>__受注日_norm</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>__工程名_norm</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>__依頼NO_norm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -691,21 +673,6 @@
       <c r="X2" t="n">
         <v>300</v>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>巻返し</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>A5-1</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -802,21 +769,6 @@
       <c r="X3" t="n">
         <v>1200</v>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>A5-2</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -913,151 +865,123 @@
       <c r="X4" t="n">
         <v>2100</v>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>接続</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>A5-2</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="D5" t="n">
+        <v>79182</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>JR260405-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7A1 </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0   </t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30020-A05W- 870X 97   LG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>97</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>97</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>SEC機　湖南</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D5" t="n">
-        <v>79063</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>JR260501</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7A1 </t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FEL4004AY-10WD-1000X100</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>300</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0   </t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>300</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>SEC,梱包,スリット</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>300</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="n">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="X5" t="n">
-        <v>300</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>JR260501</t>
-        </is>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="D6" t="n">
-        <v>79063</v>
+        <v>79145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JR260501</t>
+          <t>JR260406-1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1071,7 +995,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1080,18 +1004,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1100,14 +1024,16 @@
         </is>
       </c>
       <c r="O6" s="1" t="n">
-        <v>46143</v>
+        <v>46135</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>46139</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="R6" s="1" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1118,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1126,31 +1052,16 @@
         </is>
       </c>
       <c r="W6" s="2" t="n">
-        <v>46149</v>
+        <v>46139</v>
       </c>
       <c r="X6" t="n">
-        <v>300</v>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>JR260501</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1159,14 +1070,14 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="D7" t="n">
-        <v>78887</v>
+        <v>79063</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PN04-03</t>
+          <t>JR260501</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1176,31 +1087,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7C8 </t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t xml:space="preserve">40040-E10W- 870X 95   </t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1209,16 +1120,14 @@
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46150</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" s="1" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1229,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1237,25 +1146,10 @@
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="X7" t="n">
-        <v>2300</v>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026/04/16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>PN04-03</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
@@ -1270,159 +1164,142 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D8" t="n">
+        <v>79063</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JR260501</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7A1 </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FEL4004AY-10WD-1000X100</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>300</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0   </t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40040-E10W- 870X 95   </t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>300</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" s="1" t="n">
         <v>46132</v>
       </c>
-      <c r="D8" t="n">
-        <v>78976</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>S260420-1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 535X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>46139</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>0:未完</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W8" s="2" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="X8" t="n">
-        <v>4200</v>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>S260420-1</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="D9" t="n">
-        <v>78976</v>
+        <v>78887</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S260420-1</t>
+          <t>PN04-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6000</v>
+        <v>2300</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t xml:space="preserve">7C8 </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 535X200F-AGA1C</t>
+          <t>FEL3002BY05WDLG-EC</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6000</v>
+        <v>2300</v>
       </c>
       <c r="L9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1431,16 +1308,16 @@
         </is>
       </c>
       <c r="O9" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1448,42 +1325,27 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>6000</v>
+        <v>2300</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W9" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="X9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>S260420-1</t>
-        </is>
+        <v>2300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1492,28 +1354,28 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46135</v>
+        <v>46132</v>
       </c>
       <c r="D10" t="n">
-        <v>79141</v>
+        <v>78976</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>S260420-1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8600</v>
+        <v>6000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1522,34 +1384,36 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>0R040-8Y0B- 535X200F-AGA1C</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8600</v>
+        <v>6000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
-        <v>46153</v>
+        <v>46136</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>46143</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>46142</v>
+      </c>
       <c r="R10" s="1" t="n">
-        <v>46155</v>
+        <v>46139</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1557,10 +1421,10 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="U10" t="n">
-        <v>8600</v>
+        <v>6000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1568,25 +1432,10 @@
         </is>
       </c>
       <c r="W10" s="2" t="n">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="X10" t="n">
-        <v>5600</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>分割</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>V5-1</t>
-        </is>
+        <v>3000</v>
       </c>
     </row>
     <row r="11">
@@ -1677,47 +1526,32 @@
         </is>
       </c>
       <c r="W11" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="X11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>分割</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>V5-1</t>
-        </is>
+        <v>5600</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D12" t="n">
-        <v>79142</v>
+        <v>79141</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1731,7 +1565,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2000</v>
+        <v>8600</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1740,18 +1574,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2000</v>
+        <v>8600</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1778,33 +1612,18 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2000</v>
+        <v>8600</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W12" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>V5-2</t>
-        </is>
+        <v>3000</v>
       </c>
     </row>
     <row r="13">
@@ -1822,11 +1641,11 @@
         <v>46135</v>
       </c>
       <c r="D13" t="n">
-        <v>79143</v>
+        <v>79142</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>V5-3</t>
+          <t>V5-2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1836,11 +1655,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-ABK0C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1849,18 +1668,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1872,7 +1691,7 @@
         <v>46153</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" s="1" t="n">
@@ -1887,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1898,78 +1717,63 @@
         <v>46154</v>
       </c>
       <c r="X13" t="n">
-        <v>300</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>V5-3</t>
-        </is>
+        <v>2000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="D14" t="n">
-        <v>78623</v>
+        <v>79143</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>W4-11</t>
+          <t>V5-3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30060-AG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="L14" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1978,16 +1782,14 @@
         </is>
       </c>
       <c r="O14" s="1" t="n">
-        <v>46128</v>
+        <v>46153</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>46140</v>
-      </c>
+        <v>46156</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" s="1" t="n">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1995,36 +1797,21 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W14" s="2" t="n">
-        <v>46139</v>
+        <v>46154</v>
       </c>
       <c r="X14" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026/04/08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>W4-11</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -2042,11 +1829,11 @@
         <v>46120</v>
       </c>
       <c r="D15" t="n">
-        <v>78624</v>
+        <v>78623</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>W4-12</t>
+          <t>W4-11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2056,11 +1843,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2069,14 +1856,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2092,13 +1879,13 @@
         <v>46128</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2106,10 +1893,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="U15" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2117,25 +1904,10 @@
         </is>
       </c>
       <c r="W15" s="2" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="X15" t="n">
-        <v>3300</v>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026/04/08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>W4-12</t>
-        </is>
+        <v>600</v>
       </c>
     </row>
     <row r="16">
@@ -2228,145 +2000,117 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="X16" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026/04/08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>W4-12</t>
-        </is>
+        <v>2700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="D17" t="n">
+        <v>78624</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>W4-12</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1300X300F-A   P</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1300X300F-A   R</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5700</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5700</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D17" t="n">
-        <v>79067</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>W5-1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1250</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>EC,巻返し,欠点表示</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1250</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>EC機　湖南</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="n">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="X17" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>W5-1</t>
-        </is>
+        <v>3000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
@@ -2446,47 +2190,32 @@
         </is>
       </c>
       <c r="W18" s="2" t="n">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="X18" t="n">
         <v>1500</v>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>巻返し</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>W5-1</t>
-        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="D19" t="n">
-        <v>79138</v>
+        <v>79067</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2496,11 +2225,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6000</v>
+        <v>1250</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2509,18 +2238,18 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6000</v>
+        <v>1250</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2529,14 +2258,14 @@
         </is>
       </c>
       <c r="O19" s="1" t="n">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" s="1" t="n">
-        <v>46155</v>
+        <v>46150</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2547,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>6000</v>
+        <v>1250</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2558,22 +2287,7 @@
         <v>46153</v>
       </c>
       <c r="X19" t="n">
-        <v>4200</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>W5-2</t>
-        </is>
+        <v>1500</v>
       </c>
     </row>
     <row r="20">
@@ -2664,36 +2378,21 @@
         </is>
       </c>
       <c r="W20" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="X20" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>W5-2</t>
-        </is>
+        <v>4200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
@@ -2754,7 +2453,7 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" s="1" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2776,22 +2475,7 @@
         <v>46154</v>
       </c>
       <c r="X21" t="n">
-        <v>600</v>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>W5-2</t>
-        </is>
+        <v>1800</v>
       </c>
     </row>
     <row r="22">
@@ -2882,25 +2566,10 @@
         </is>
       </c>
       <c r="W22" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="X22" t="n">
-        <v>3300</v>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>W5-2</t>
-        </is>
+        <v>600</v>
       </c>
     </row>
     <row r="23">
@@ -2991,47 +2660,32 @@
         </is>
       </c>
       <c r="W23" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="X23" t="n">
-        <v>2100</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>W5-2</t>
-        </is>
+        <v>3300</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D24" t="n">
-        <v>79139</v>
+        <v>79138</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3077,11 +2731,11 @@
         <v>46153</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3100,25 +2754,10 @@
         </is>
       </c>
       <c r="W24" s="2" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="X24" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>W5-3</t>
-        </is>
+        <v>2100</v>
       </c>
     </row>
     <row r="25">
@@ -3209,36 +2848,21 @@
         </is>
       </c>
       <c r="W25" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="X25" t="n">
-        <v>4500</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>W5-3</t>
-        </is>
+        <v>1500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
@@ -3299,7 +2923,7 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3318,25 +2942,10 @@
         </is>
       </c>
       <c r="W26" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="X26" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>W5-3</t>
-        </is>
+        <v>4500</v>
       </c>
     </row>
     <row r="27">
@@ -3427,25 +3036,10 @@
         </is>
       </c>
       <c r="W27" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="X27" t="n">
-        <v>3300</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>W5-3</t>
-        </is>
+        <v>1200</v>
       </c>
     </row>
     <row r="28">
@@ -3536,47 +3130,32 @@
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="X28" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>W5-3</t>
-        </is>
+        <v>3300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C29" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D29" t="n">
-        <v>79140</v>
+        <v>79139</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3586,11 +3165,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3599,11 +3178,11 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3619,14 +3198,14 @@
         </is>
       </c>
       <c r="O29" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3637,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3645,25 +3224,10 @@
         </is>
       </c>
       <c r="W29" s="2" t="n">
-        <v>46149</v>
+        <v>46160</v>
       </c>
       <c r="X29" t="n">
-        <v>4200</v>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>W5-4</t>
-        </is>
+        <v>1500</v>
       </c>
     </row>
     <row r="30">
@@ -3754,36 +3318,21 @@
         </is>
       </c>
       <c r="W30" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X30" t="n">
-        <v>4800</v>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>W5-4</t>
-        </is>
+        <v>4200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
@@ -3844,7 +3393,7 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" s="1" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3863,25 +3412,10 @@
         </is>
       </c>
       <c r="W31" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="X31" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>W5-4</t>
-        </is>
+        <v>4800</v>
       </c>
     </row>
     <row r="32">
@@ -3972,25 +3506,10 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X32" t="n">
-        <v>3300</v>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>W5-4</t>
-        </is>
+        <v>1500</v>
       </c>
     </row>
     <row r="33">
@@ -4081,25 +3600,10 @@
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="X33" t="n">
         <v>3300</v>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>W5-4</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -4190,81 +3694,66 @@
         </is>
       </c>
       <c r="W34" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="X34" t="n">
-        <v>900</v>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026/04/23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>W5-4</t>
-        </is>
+        <v>3300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="D35" t="n">
-        <v>78822</v>
+        <v>79140</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Y4-49</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4273,16 +3762,14 @@
         </is>
       </c>
       <c r="O35" s="1" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q35" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" s="1" t="n">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -4293,33 +3780,18 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W35" s="2" t="n">
-        <v>46139</v>
+        <v>46154</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Y4-49</t>
-        </is>
+        <v>900</v>
       </c>
     </row>
     <row r="36">
@@ -4337,11 +3809,11 @@
         <v>46127</v>
       </c>
       <c r="D36" t="n">
-        <v>78823</v>
+        <v>78822</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Y4-50</t>
+          <t>Y4-49</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4351,7 +3823,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -4375,7 +3847,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4384,7 +3856,7 @@
         </is>
       </c>
       <c r="O36" s="1" t="n">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>46142</v>
@@ -4408,7 +3880,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W36" s="2" t="n">
@@ -4416,32 +3888,17 @@
       </c>
       <c r="X36" t="n">
         <v>1000</v>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Y4-50</t>
-        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C37" s="1" t="n">
@@ -4523,47 +3980,32 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>接続</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Y4-50</t>
-        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
         <v>46127</v>
       </c>
       <c r="D38" t="n">
-        <v>78826</v>
+        <v>78823</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Y4-51</t>
+          <t>Y4-50</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4573,7 +4015,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4586,7 +4028,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -4597,16 +4039,16 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="P38" s="1" t="n">
         <v>46142</v>
@@ -4628,49 +4070,38 @@
       <c r="U38" t="n">
         <v>1000</v>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
       <c r="W38" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Y4-51</t>
-        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
         <v>46127</v>
       </c>
       <c r="D39" t="n">
-        <v>78826</v>
+        <v>78827</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Y4-51</t>
+          <t>Y4-52</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4684,7 +4115,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4693,18 +4124,18 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="L39" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4722,40 +4153,29 @@
         <v>46142</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="T39" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V39" t="inlineStr"/>
+        <v>2200</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
       <c r="W39" s="2" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Y4-51</t>
-        </is>
+        <v>2200</v>
       </c>
     </row>
     <row r="40">
@@ -4773,11 +4193,11 @@
         <v>46127</v>
       </c>
       <c r="D40" t="n">
-        <v>78827</v>
+        <v>78828</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Y4-52</t>
+          <t>Y4-53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4787,11 +4207,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4800,11 +4220,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4816,11 +4236,11 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="P40" s="1" t="n">
         <v>46142</v>
@@ -4840,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4851,22 +4271,7 @@
         <v>46139</v>
       </c>
       <c r="X40" t="n">
-        <v>2200</v>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Y4-52</t>
-        </is>
+        <v>1000</v>
       </c>
     </row>
     <row r="41">
@@ -4884,11 +4289,11 @@
         <v>46127</v>
       </c>
       <c r="D41" t="n">
-        <v>78828</v>
+        <v>78846</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Y4-53</t>
+          <t>Y4-54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4898,11 +4303,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4915,14 +4320,14 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4931,7 +4336,7 @@
         </is>
       </c>
       <c r="O41" s="1" t="n">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>46142</v>
@@ -4951,44 +4356,29 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Y4-53</t>
-        </is>
+        <v>600</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
@@ -5074,43 +4464,28 @@
       </c>
       <c r="X42" t="n">
         <v>600</v>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Y4-54</t>
-        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="D43" t="n">
-        <v>78846</v>
+        <v>79018</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Y4-54</t>
+          <t>Y4-58</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5120,11 +4495,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5133,36 +4508,34 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q43" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46149</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -5173,55 +4546,40 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="X43" t="n">
-        <v>600</v>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>接続</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Y4-54</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="D44" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Y4-58</t>
+          <t>Y4-59</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5231,11 +4589,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>400</v>
+        <v>7500</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5244,18 +4602,18 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>400</v>
+        <v>7500</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5267,7 +4625,7 @@
         <v>46143</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" s="1" t="n">
@@ -5282,33 +4640,18 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>400</v>
+        <v>7500</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W44" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="X44" t="n">
-        <v>400</v>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026/04/21</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>分割</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Y4-58</t>
-        </is>
+        <v>5100</v>
       </c>
     </row>
     <row r="45">
@@ -5399,25 +4742,10 @@
         </is>
       </c>
       <c r="W45" s="2" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="X45" t="n">
-        <v>5100</v>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026/04/21</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Y4-59</t>
-        </is>
+        <v>2400</v>
       </c>
     </row>
     <row r="46">
@@ -5432,14 +4760,14 @@
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46133</v>
+        <v>46106</v>
       </c>
       <c r="D46" t="n">
-        <v>79019</v>
+        <v>78074</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Y4-59</t>
+          <t>Y4-7</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5449,11 +4777,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -5462,14 +4790,14 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -5478,18 +4806,20 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
-        <v>46143</v>
+        <v>46135</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+        <v>46140</v>
+      </c>
+      <c r="Q46" s="1" t="n">
+        <v>46140</v>
+      </c>
       <c r="R46" s="1" t="n">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -5497,10 +4827,10 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="U46" t="n">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -5508,25 +4838,10 @@
         </is>
       </c>
       <c r="W46" s="2" t="n">
-        <v>46149</v>
+        <v>46139</v>
       </c>
       <c r="X46" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026/04/21</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Y4-59</t>
-        </is>
+        <v>3000</v>
       </c>
     </row>
     <row r="47">
@@ -5541,14 +4856,14 @@
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="D47" t="n">
-        <v>78074</v>
+        <v>79070</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Y4-7</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5558,11 +4873,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5571,14 +4886,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="L47" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -5591,16 +4906,14 @@
         </is>
       </c>
       <c r="O47" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="Q47" s="1" t="n">
-        <v>46140</v>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -5608,10 +4921,10 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -5619,25 +4932,10 @@
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="X47" t="n">
-        <v>7200</v>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026/03/25</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Y4-7</t>
-        </is>
+        <v>3600</v>
       </c>
     </row>
     <row r="48">
@@ -5728,25 +5026,10 @@
         </is>
       </c>
       <c r="W48" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="X48" t="n">
-        <v>3600</v>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Y5-1</t>
-        </is>
+        <v>600</v>
       </c>
     </row>
     <row r="49">
@@ -5837,25 +5120,10 @@
         </is>
       </c>
       <c r="W49" s="2" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="X49" t="n">
-        <v>600</v>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Y5-1</t>
-        </is>
+        <v>4800</v>
       </c>
     </row>
     <row r="50">
@@ -5873,11 +5141,11 @@
         <v>46134</v>
       </c>
       <c r="D50" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5920,10 +5188,10 @@
         </is>
       </c>
       <c r="O50" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" s="1" t="n">
@@ -5949,22 +5217,7 @@
         <v>46153</v>
       </c>
       <c r="X50" t="n">
-        <v>4800</v>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Y5-1</t>
-        </is>
+        <v>3300</v>
       </c>
     </row>
     <row r="51">
@@ -6055,47 +5308,32 @@
         </is>
       </c>
       <c r="W51" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="X51" t="n">
-        <v>3300</v>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Y5-2</t>
-        </is>
+        <v>5700</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D52" t="n">
-        <v>79071</v>
+        <v>79072</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>Y5-3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6105,11 +5343,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9000</v>
+        <v>2299</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -6118,18 +5356,18 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9000</v>
+        <v>2299</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6138,14 +5376,14 @@
         </is>
       </c>
       <c r="O52" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="P52" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" s="1" t="n">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -6156,44 +5394,29 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>9000</v>
+        <v>2299</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W52" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X52" t="n">
-        <v>5700</v>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Y5-2</t>
-        </is>
+        <v>2400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C53" s="1" t="n">
@@ -6254,7 +5477,7 @@
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -6277,43 +5500,28 @@
       </c>
       <c r="X53" t="n">
         <v>2400</v>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Y5-3</t>
-        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D54" t="n">
-        <v>79072</v>
+        <v>79075</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>Y5-4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6323,11 +5531,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2299</v>
+        <v>200</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6336,11 +5544,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>2299</v>
+        <v>200</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6359,11 +5567,11 @@
         <v>46149</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -6374,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2299</v>
+        <v>200</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -6385,33 +5593,18 @@
         <v>46154</v>
       </c>
       <c r="X54" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>接続</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Y5-3</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C55" s="1" t="n">
@@ -6472,7 +5665,7 @@
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -6495,43 +5688,28 @@
       </c>
       <c r="X55" t="n">
         <v>200</v>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Y5-4</t>
-        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Y5-4</t>
+          <t>Y5-5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6541,11 +5719,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6558,14 +5736,14 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6581,44 +5759,29 @@
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>200</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>熱融着機　湖南</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="n">
-        <v>46154</v>
-      </c>
       <c r="X56" t="n">
-        <v>200</v>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>接続</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Y5-4</t>
-        </is>
+        <v>1200</v>
       </c>
     </row>
     <row r="57">
@@ -6636,11 +5799,11 @@
         <v>46134</v>
       </c>
       <c r="D57" t="n">
-        <v>79076</v>
+        <v>79077</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Y5-5</t>
+          <t>Y5-6</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6650,11 +5813,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6663,18 +5826,18 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6701,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -6712,33 +5875,18 @@
         <v>46150</v>
       </c>
       <c r="X57" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Y5-5</t>
-        </is>
+        <v>2000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
@@ -6799,7 +5947,7 @@
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6818,47 +5966,32 @@
         </is>
       </c>
       <c r="W58" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X58" t="n">
         <v>2000</v>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Y5-6</t>
-        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="D59" t="n">
-        <v>79077</v>
+        <v>79148</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Y5-6</t>
+          <t>Y5-7</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6868,11 +6001,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6881,34 +6014,34 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6919,33 +6052,112 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W59" s="2" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="X59" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Y5-6</t>
-        </is>
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="D60" t="n">
+        <v>79148</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Y5-7</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>30044-AG00-1000X200F-AWH1C</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>30022-BG00-1000X200F-AWH1C</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="O60" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="X60" t="n">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -132,8 +132,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:X60" headerRowCount="1">
-  <autoFilter ref="A1:X60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:X61" headerRowCount="1">
+  <autoFilter ref="A1:X61"/>
   <tableColumns count="24">
     <tableColumn id="1" name="工程名"/>
     <tableColumn id="2" name="機械名"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,7 +767,7 @@
         <v>46153</v>
       </c>
       <c r="X3" t="n">
-        <v>1200</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="4">
@@ -959,7 +959,7 @@
         <v>46139</v>
       </c>
       <c r="X5" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
@@ -2851,7 +2851,7 @@
         <v>46154</v>
       </c>
       <c r="X25" t="n">
-        <v>1500</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="26">
@@ -2945,7 +2945,7 @@
         <v>46155</v>
       </c>
       <c r="X26" t="n">
-        <v>4500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="27">
@@ -4097,11 +4097,11 @@
         <v>46127</v>
       </c>
       <c r="D39" t="n">
-        <v>78827</v>
+        <v>78826</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Y4-52</t>
+          <t>Y4-51</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4124,18 +4124,18 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4164,18 +4164,14 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2200</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="X39" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40">
@@ -4193,11 +4189,11 @@
         <v>46127</v>
       </c>
       <c r="D40" t="n">
-        <v>78828</v>
+        <v>78827</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Y4-53</t>
+          <t>Y4-52</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4207,11 +4203,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4220,11 +4216,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4236,11 +4232,11 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="P40" s="1" t="n">
         <v>46142</v>
@@ -4260,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4271,7 +4267,7 @@
         <v>46139</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="41">
@@ -4289,11 +4285,11 @@
         <v>46127</v>
       </c>
       <c r="D41" t="n">
-        <v>78846</v>
+        <v>78828</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Y4-54</t>
+          <t>Y4-53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4303,11 +4299,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4320,14 +4316,14 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4336,7 +4332,7 @@
         </is>
       </c>
       <c r="O41" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>46142</v>
@@ -4356,29 +4352,29 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="X41" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
@@ -4469,23 +4465,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="D43" t="n">
-        <v>79018</v>
+        <v>78846</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Y4-58</t>
+          <t>Y4-54</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4495,11 +4491,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4508,34 +4504,36 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+        <v>46142</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>46142</v>
+      </c>
       <c r="R43" s="1" t="n">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4546,40 +4544,40 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="X43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="D44" t="n">
-        <v>79019</v>
+        <v>79018</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Y4-59</t>
+          <t>Y4-58</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4589,11 +4587,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7500</v>
+        <v>400</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4602,18 +4600,18 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>7500</v>
+        <v>400</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4625,7 +4623,7 @@
         <v>46143</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" s="1" t="n">
@@ -4640,18 +4638,18 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>7500</v>
+        <v>400</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W44" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="X44" t="n">
-        <v>5100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45">
@@ -4742,10 +4740,10 @@
         </is>
       </c>
       <c r="W45" s="2" t="n">
-        <v>46149</v>
+        <v>46143</v>
       </c>
       <c r="X45" t="n">
-        <v>2400</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="46">
@@ -4760,14 +4758,14 @@
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="D46" t="n">
-        <v>78074</v>
+        <v>79019</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Y4-7</t>
+          <t>Y4-59</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4777,11 +4775,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>9400</v>
+        <v>7500</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4790,14 +4788,14 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9400</v>
+        <v>7500</v>
       </c>
       <c r="L46" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4806,20 +4804,18 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="Q46" s="1" t="n">
-        <v>46140</v>
-      </c>
+        <v>46150</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4827,10 +4823,10 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>9400</v>
+        <v>7500</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4838,10 +4834,10 @@
         </is>
       </c>
       <c r="W46" s="2" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="X46" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="47">
@@ -4856,14 +4852,14 @@
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46134</v>
+        <v>46106</v>
       </c>
       <c r="D47" t="n">
-        <v>79070</v>
+        <v>78074</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y4-7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4873,11 +4869,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9000</v>
+        <v>9400</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4886,14 +4882,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9000</v>
+        <v>9400</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4906,14 +4902,16 @@
         </is>
       </c>
       <c r="O47" s="1" t="n">
-        <v>46149</v>
+        <v>46135</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+        <v>46140</v>
+      </c>
+      <c r="Q47" s="1" t="n">
+        <v>46140</v>
+      </c>
       <c r="R47" s="1" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4921,10 +4919,10 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="U47" t="n">
-        <v>9000</v>
+        <v>9400</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4932,10 +4930,10 @@
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>46149</v>
+        <v>46139</v>
       </c>
       <c r="X47" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="48">
@@ -5026,10 +5024,10 @@
         </is>
       </c>
       <c r="W48" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X48" t="n">
-        <v>600</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="49">
@@ -5120,10 +5118,10 @@
         </is>
       </c>
       <c r="W49" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="X49" t="n">
-        <v>4800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="50">
@@ -5141,11 +5139,11 @@
         <v>46134</v>
       </c>
       <c r="D50" t="n">
-        <v>79071</v>
+        <v>79070</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5188,10 +5186,10 @@
         </is>
       </c>
       <c r="O50" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" s="1" t="n">
@@ -5217,7 +5215,7 @@
         <v>46153</v>
       </c>
       <c r="X50" t="n">
-        <v>3300</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="51">
@@ -5308,32 +5306,32 @@
         </is>
       </c>
       <c r="W51" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="X51" t="n">
-        <v>5700</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D52" t="n">
-        <v>79072</v>
+        <v>79071</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>Y5-2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5343,11 +5341,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2299</v>
+        <v>9000</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5356,18 +5354,18 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>2299</v>
+        <v>9000</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5376,14 +5374,14 @@
         </is>
       </c>
       <c r="O52" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="P52" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" s="1" t="n">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5394,29 +5392,29 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2299</v>
+        <v>9000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W52" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X52" t="n">
-        <v>2400</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C53" s="1" t="n">
@@ -5477,7 +5475,7 @@
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5505,23 +5503,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D54" t="n">
-        <v>79075</v>
+        <v>79072</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Y5-4</t>
+          <t>Y5-3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5531,11 +5529,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
+          <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>200</v>
+        <v>2299</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5544,11 +5542,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>200</v>
+        <v>2299</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -5567,11 +5565,11 @@
         <v>46149</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5582,7 +5580,7 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>200</v>
+        <v>2299</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -5593,18 +5591,18 @@
         <v>46154</v>
       </c>
       <c r="X54" t="n">
-        <v>200</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C55" s="1" t="n">
@@ -5665,7 +5663,7 @@
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5693,23 +5691,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D56" t="n">
-        <v>79076</v>
+        <v>79075</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Y5-5</t>
+          <t>Y5-4</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5719,11 +5717,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5736,14 +5734,14 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5759,7 +5757,7 @@
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5770,18 +5768,18 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W56" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="X56" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57">
@@ -5799,11 +5797,11 @@
         <v>46134</v>
       </c>
       <c r="D57" t="n">
-        <v>79077</v>
+        <v>79076</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Y5-6</t>
+          <t>Y5-5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5813,11 +5811,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5826,18 +5824,18 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5864,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -5875,18 +5873,18 @@
         <v>46150</v>
       </c>
       <c r="X57" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
@@ -5947,7 +5945,7 @@
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5966,7 +5964,7 @@
         </is>
       </c>
       <c r="W58" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="X58" t="n">
         <v>2000</v>
@@ -5975,23 +5973,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="D59" t="n">
-        <v>79148</v>
+        <v>79077</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Y5-7</t>
+          <t>Y5-6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6001,11 +5999,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6014,34 +6012,34 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
-        <v>46155</v>
+        <v>46149</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" s="1" t="n">
-        <v>46156</v>
+        <v>46150</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6052,18 +6050,18 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W59" s="2" t="n">
-        <v>46155</v>
+        <v>46149</v>
       </c>
       <c r="X59" t="n">
-        <v>5600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="60">
@@ -6154,9 +6152,103 @@
         </is>
       </c>
       <c r="W60" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="X60" t="n">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="D61" t="n">
+        <v>79148</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Y5-7</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>30044-AG00-1000X200F-AWH1C</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>30022-BG00-1000X200F-AWH1C</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="X60" t="n">
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="X61" t="n">
         <v>400</v>
       </c>
     </row>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -767,7 +767,7 @@
         <v>46153</v>
       </c>
       <c r="X3" t="n">
-        <v>1155</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="4">
@@ -2193,7 +2193,7 @@
         <v>46143</v>
       </c>
       <c r="X18" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="19">
@@ -2287,7 +2287,7 @@
         <v>46153</v>
       </c>
       <c r="X19" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="20">
@@ -5309,7 +5309,7 @@
         <v>46153</v>
       </c>
       <c r="X51" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="52">
@@ -5403,7 +5403,7 @@
         <v>46154</v>
       </c>
       <c r="X52" t="n">
-        <v>5700</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="53">

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="結果_配台表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="結果_配台表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="X16" t="n">
-        <v>2700</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="17">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="W17" s="2" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="X17" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="18">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="W38" s="2" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="X42" t="n">
         <v>600</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="X43" t="n">
         <v>600</v>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -132,8 +132,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:X61" headerRowCount="1">
-  <autoFilter ref="A1:X61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_t結果_配台表" displayName="_t結果_配台表" ref="A1:X54" headerRowCount="1">
+  <autoFilter ref="A1:X54"/>
   <tableColumns count="24">
     <tableColumn id="1" name="工程名"/>
     <tableColumn id="2" name="機械名"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="W2" s="2" t="n">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="X2" t="n">
         <v>300</v>
@@ -869,23 +869,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="D5" t="n">
-        <v>79182</v>
+        <v>79063</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JR260405-1</t>
+          <t>JR260501</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -895,11 +895,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -908,18 +908,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t xml:space="preserve">40040-E10W- 870X 95   </t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,16 +928,14 @@
         </is>
       </c>
       <c r="O5" s="1" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>46140</v>
-      </c>
+        <v>46150</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -956,32 +954,32 @@
         </is>
       </c>
       <c r="W5" s="2" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="X5" t="n">
-        <v>190</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="D6" t="n">
-        <v>79145</v>
+        <v>79063</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JR260406-1</t>
+          <t>JR260501</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -995,7 +993,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1004,18 +1002,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95</t>
+          <t xml:space="preserve">40040-E10W- 870X 95   </t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,16 +1022,14 @@
         </is>
       </c>
       <c r="O6" s="1" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>46139</v>
-      </c>
+        <v>46150</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1044,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1052,16 +1048,16 @@
         </is>
       </c>
       <c r="W6" s="2" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="X6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,14 +1066,14 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="D7" t="n">
-        <v>79063</v>
+        <v>78887</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JR260501</t>
+          <t>PN04-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1087,31 +1083,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>FEL3002BY05-10WD-1000X100   LG</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>300</v>
+        <v>2300</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0   </t>
+          <t xml:space="preserve">7C8 </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
+          <t>FEL3002BY05WDLG-EC</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>300</v>
+        <v>2300</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>梱包,EC</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1120,14 +1116,16 @@
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>46142</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>46142</v>
+      </c>
       <c r="R7" s="1" t="n">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1138,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>300</v>
+        <v>2300</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1146,16 +1144,16 @@
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="X7" t="n">
-        <v>300</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1164,64 +1162,64 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D8" t="n">
-        <v>79063</v>
+        <v>79141</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JR260501</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>300</v>
+        <v>8600</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0   </t>
+          <t>6713</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">40040-E10W- 870X 95   </t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>300</v>
+        <v>8600</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" s="1" t="n">
-        <v>46132</v>
+        <v>46155</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,92 +1230,90 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>300</v>
+        <v>8600</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W8" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="X8" t="n">
-        <v>300</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="D9" t="n">
-        <v>78887</v>
+        <v>79141</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PN04-03</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7C8 </t>
+          <t>6713</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46157</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" s="1" t="n">
-        <v>46140</v>
+        <v>46155</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1328,24 +1324,24 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W9" s="2" t="n">
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="X9" t="n">
-        <v>2300</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1354,66 +1350,64 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="D10" t="n">
-        <v>78976</v>
+        <v>79141</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S260420-1</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30060-AG00-1000X200F-A   C</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>8600</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>6713</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 535X200F-AGA1C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6000</v>
+        <v>8600</v>
       </c>
       <c r="L10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
-        <v>46136</v>
+        <v>46153</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46157</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" s="1" t="n">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1421,10 +1415,10 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>6000</v>
+        <v>8600</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1432,32 +1426,32 @@
         </is>
       </c>
       <c r="W10" s="2" t="n">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="X10" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D11" t="n">
-        <v>79141</v>
+        <v>79142</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>V5-2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1471,7 +1465,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8600</v>
+        <v>2000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1480,18 +1474,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8600</v>
+        <v>2000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1518,40 +1512,40 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>8600</v>
+        <v>2000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W11" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="X11" t="n">
-        <v>5600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D12" t="n">
-        <v>79141</v>
+        <v>79143</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>V5-3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1561,11 +1555,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30060-AG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1574,18 +1568,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,7 +1591,7 @@
         <v>46153</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" s="1" t="n">
@@ -1612,74 +1606,74 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W12" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X12" t="n">
-        <v>3000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46135</v>
+        <v>46120</v>
       </c>
       <c r="D13" t="n">
-        <v>79142</v>
+        <v>78624</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>W4-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1688,14 +1682,16 @@
         </is>
       </c>
       <c r="O13" s="1" t="n">
-        <v>46153</v>
+        <v>46128</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>46142</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>46142</v>
+      </c>
       <c r="R13" s="1" t="n">
-        <v>46155</v>
+        <v>46141</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1703,77 +1699,77 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="U13" t="n">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W13" s="2" t="n">
-        <v>46154</v>
+        <v>46140</v>
       </c>
       <c r="X13" t="n">
-        <v>2000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46135</v>
+        <v>46120</v>
       </c>
       <c r="D14" t="n">
-        <v>79143</v>
+        <v>78624</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>V5-3</t>
+          <t>W4-12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-ABK0C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>300</v>
+        <v>5700</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>300</v>
+        <v>5700</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1782,14 +1778,16 @@
         </is>
       </c>
       <c r="O14" s="1" t="n">
-        <v>46153</v>
+        <v>46128</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>46142</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>46142</v>
+      </c>
       <c r="R14" s="1" t="n">
-        <v>46155</v>
+        <v>46141</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1797,43 +1795,43 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="U14" t="n">
-        <v>300</v>
+        <v>5700</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W14" s="2" t="n">
-        <v>46154</v>
+        <v>46141</v>
       </c>
       <c r="X14" t="n">
-        <v>300</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="D15" t="n">
-        <v>78623</v>
+        <v>79067</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>W4-11</t>
+          <t>W5-1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1843,11 +1841,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6000</v>
+        <v>1250</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1856,36 +1854,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6000</v>
+        <v>1250</v>
       </c>
       <c r="L15" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
-        <v>46128</v>
+        <v>46143</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>46140</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1893,10 +1889,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>6000</v>
+        <v>1250</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1904,32 +1900,32 @@
         </is>
       </c>
       <c r="W15" s="2" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="X15" t="n">
-        <v>600</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="D16" t="n">
-        <v>78624</v>
+        <v>79067</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>W4-12</t>
+          <t>W5-1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1939,11 +1935,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5700</v>
+        <v>1250</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1952,36 +1948,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5700</v>
+        <v>1250</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
-        <v>46128</v>
+        <v>46143</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1992,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5700</v>
+        <v>1250</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2000,32 +1994,32 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="X16" t="n">
-        <v>3300</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="D17" t="n">
-        <v>78624</v>
+        <v>79138</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>W4-12</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2039,7 +2033,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2052,7 +2046,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2068,16 +2062,14 @@
         </is>
       </c>
       <c r="O17" s="1" t="n">
-        <v>46128</v>
+        <v>46153</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46156</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" s="1" t="n">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2088,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="W17" s="2" t="n">
-        <v>46141</v>
+        <v>46153</v>
       </c>
       <c r="X17" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="18">
@@ -2114,14 +2106,14 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D18" t="n">
-        <v>79067</v>
+        <v>79138</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>W5-1</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2131,11 +2123,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2144,18 +2136,18 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2164,14 +2156,14 @@
         </is>
       </c>
       <c r="O18" s="1" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" s="1" t="n">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2182,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2190,32 +2182,32 @@
         </is>
       </c>
       <c r="W18" s="2" t="n">
-        <v>46143</v>
+        <v>46154</v>
       </c>
       <c r="X18" t="n">
-        <v>1250</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D19" t="n">
-        <v>79067</v>
+        <v>79138</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W5-1</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2225,11 +2217,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2238,18 +2230,18 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2258,14 +2250,14 @@
         </is>
       </c>
       <c r="O19" s="1" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" s="1" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2276,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2284,21 +2276,21 @@
         </is>
       </c>
       <c r="W19" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="X19" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2378,21 +2370,21 @@
         </is>
       </c>
       <c r="W20" s="2" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="X20" t="n">
-        <v>4200</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
@@ -2453,7 +2445,7 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2472,32 +2464,32 @@
         </is>
       </c>
       <c r="W21" s="2" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="X21" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D22" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2543,11 +2535,11 @@
         <v>46153</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" s="1" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2569,29 +2561,29 @@
         <v>46154</v>
       </c>
       <c r="X22" t="n">
-        <v>600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C23" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D23" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2637,11 +2629,11 @@
         <v>46153</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" s="1" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2660,10 +2652,10 @@
         </is>
       </c>
       <c r="W23" s="2" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="X23" t="n">
-        <v>3300</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="24">
@@ -2681,11 +2673,11 @@
         <v>46135</v>
       </c>
       <c r="D24" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2731,11 +2723,11 @@
         <v>46153</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2757,18 +2749,18 @@
         <v>46156</v>
       </c>
       <c r="X24" t="n">
-        <v>2100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C25" s="1" t="n">
@@ -2829,7 +2821,7 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2848,21 +2840,21 @@
         </is>
       </c>
       <c r="W25" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="X25" t="n">
-        <v>2400</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
@@ -2923,7 +2915,7 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2942,32 +2934,32 @@
         </is>
       </c>
       <c r="W26" s="2" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="X26" t="n">
-        <v>3600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C27" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D27" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2977,11 +2969,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2990,11 +2982,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3010,14 +3002,14 @@
         </is>
       </c>
       <c r="O27" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" s="1" t="n">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3028,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -3036,32 +3028,32 @@
         </is>
       </c>
       <c r="W27" s="2" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="X27" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D28" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3071,11 +3063,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3084,11 +3076,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3104,14 +3096,14 @@
         </is>
       </c>
       <c r="O28" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" s="1" t="n">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3122,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3130,10 +3122,10 @@
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="X28" t="n">
-        <v>3300</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="29">
@@ -3151,11 +3143,11 @@
         <v>46135</v>
       </c>
       <c r="D29" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3165,11 +3157,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3178,11 +3170,11 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3198,14 +3190,14 @@
         </is>
       </c>
       <c r="O29" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3216,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3224,7 +3216,7 @@
         </is>
       </c>
       <c r="W29" s="2" t="n">
-        <v>46160</v>
+        <v>46149</v>
       </c>
       <c r="X29" t="n">
         <v>1500</v>
@@ -3233,12 +3225,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
@@ -3299,7 +3291,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3318,21 +3310,21 @@
         </is>
       </c>
       <c r="W30" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="X30" t="n">
-        <v>4200</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
@@ -3393,7 +3385,7 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3412,10 +3404,10 @@
         </is>
       </c>
       <c r="W31" s="2" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="X31" t="n">
-        <v>4800</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="32">
@@ -3506,82 +3498,82 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="X32" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="D33" t="n">
-        <v>79140</v>
+        <v>79018</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y4-58</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="P33" s="1" t="n">
         <v>46149</v>
-      </c>
-      <c r="P33" s="1" t="n">
-        <v>46154</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" s="1" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3592,90 +3584,90 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="X33" t="n">
-        <v>3300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="D34" t="n">
-        <v>79140</v>
+        <v>79019</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y4-59</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
-        <v>46149</v>
+        <v>46143</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" s="1" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3686,90 +3678,90 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W34" s="2" t="n">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="X34" t="n">
-        <v>3300</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="D35" t="n">
-        <v>79140</v>
+        <v>79019</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y4-59</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
-        <v>46149</v>
+        <v>46143</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" s="1" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3780,40 +3772,40 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W35" s="2" t="n">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="X35" t="n">
-        <v>900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="D36" t="n">
-        <v>78822</v>
+        <v>79070</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Y4-49</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3823,11 +3815,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3836,18 +3828,18 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3856,16 +3848,14 @@
         </is>
       </c>
       <c r="O36" s="1" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q36" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3876,40 +3866,40 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W36" s="2" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="D37" t="n">
-        <v>78823</v>
+        <v>79070</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Y4-50</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3919,11 +3909,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3932,18 +3922,18 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3952,16 +3942,14 @@
         </is>
       </c>
       <c r="O37" s="1" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q37" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3972,40 +3960,40 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="D38" t="n">
-        <v>78823</v>
+        <v>79070</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Y4-50</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4015,11 +4003,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4028,18 +4016,18 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4048,16 +4036,14 @@
         </is>
       </c>
       <c r="O38" s="1" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q38" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4068,40 +4054,40 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W38" s="2" t="n">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46127</v>
+        <v>46139</v>
       </c>
       <c r="D39" t="n">
-        <v>78826</v>
+        <v>79232</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Y4-51</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4111,11 +4097,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4124,18 +4110,18 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4144,16 +4130,16 @@
         </is>
       </c>
       <c r="O39" s="1" t="n">
-        <v>46135</v>
+        <v>46155</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46139</v>
+        <v>46156</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4164,36 +4150,40 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V39" t="inlineStr"/>
+        <v>3600</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>エンボス　湖南</t>
+        </is>
+      </c>
       <c r="W39" s="2" t="n">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46127</v>
+        <v>46139</v>
       </c>
       <c r="D40" t="n">
-        <v>78827</v>
+        <v>79232</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Y4-52</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4203,11 +4193,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2200</v>
+        <v>3600</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4216,18 +4206,18 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2200</v>
+        <v>3600</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4236,16 +4226,16 @@
         </is>
       </c>
       <c r="O40" s="1" t="n">
-        <v>46135</v>
+        <v>46155</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46139</v>
+        <v>46156</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4256,40 +4246,40 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2200</v>
+        <v>3600</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="W40" s="2" t="n">
-        <v>46139</v>
+        <v>46156</v>
       </c>
       <c r="X40" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="D41" t="n">
-        <v>78828</v>
+        <v>79071</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Y4-53</t>
+          <t>Y5-2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4299,11 +4289,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4312,18 +4302,18 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4332,16 +4322,14 @@
         </is>
       </c>
       <c r="O41" s="1" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q41" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4352,40 +4340,40 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="D42" t="n">
-        <v>78846</v>
+        <v>79071</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Y4-54</t>
+          <t>Y5-2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4395,11 +4383,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>600</v>
+        <v>9000</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4408,18 +4396,18 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>600</v>
+        <v>9000</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4428,16 +4416,14 @@
         </is>
       </c>
       <c r="O42" s="1" t="n">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q42" s="1" t="n">
-        <v>46142</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" s="1" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4448,136 +4434,134 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>600</v>
+        <v>9000</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="X42" t="n">
-        <v>600</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D43" t="n">
+        <v>79072</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Y5-3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>50080-AY0B- 870X200F-A   F</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>2299</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2299</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>接続,SEC</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2299</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>熱融着機　湖南</t>
         </is>
       </c>
-      <c r="C43" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="D43" t="n">
-        <v>78846</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Y4-54</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>600</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>600</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>接続,SEC</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="Q43" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="R43" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>600</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>熱融着機　湖南</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="n">
-        <v>46139</v>
+        <v>46154</v>
       </c>
       <c r="X43" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D44" t="n">
-        <v>79018</v>
+        <v>79072</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Y4-58</t>
+          <t>Y5-3</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4587,11 +4571,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50080-AY0B- 870X200F-A   F</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>400</v>
+        <v>2299</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4600,34 +4584,34 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>400</v>
+        <v>2299</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" s="1" t="n">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4638,40 +4622,40 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>400</v>
+        <v>2299</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W44" s="2" t="n">
-        <v>46143</v>
+        <v>46154</v>
       </c>
       <c r="X44" t="n">
-        <v>400</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D45" t="n">
-        <v>79019</v>
+        <v>79075</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Y4-59</t>
+          <t>Y5-4</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4681,11 +4665,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4694,34 +4678,34 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" s="1" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4732,40 +4716,40 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W45" s="2" t="n">
-        <v>46143</v>
+        <v>46154</v>
       </c>
       <c r="X45" t="n">
-        <v>5100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D46" t="n">
-        <v>79019</v>
+        <v>79075</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Y4-59</t>
+          <t>Y5-4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4775,11 +4759,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 680X200F-AGA1F</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4788,34 +4772,34 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" s="1" t="n">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4826,40 +4810,40 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="W46" s="2" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="X46" t="n">
-        <v>2400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="D47" t="n">
-        <v>78074</v>
+        <v>79076</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Y4-7</t>
+          <t>Y5-5</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4869,11 +4853,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9400</v>
+        <v>1200</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4882,18 +4866,18 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9400</v>
+        <v>1200</v>
       </c>
       <c r="L47" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4902,16 +4886,14 @@
         </is>
       </c>
       <c r="O47" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="Q47" s="1" t="n">
-        <v>46140</v>
-      </c>
+        <v>46154</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" s="1" t="n">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4919,43 +4901,43 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>9400</v>
+        <v>1200</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="X47" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D48" t="n">
-        <v>79070</v>
+        <v>79077</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-6</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4965,11 +4947,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4978,18 +4960,18 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5005,7 +4987,7 @@
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" s="1" t="n">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5016,40 +4998,40 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W48" s="2" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="X48" t="n">
-        <v>3600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C49" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="D49" t="n">
-        <v>79070</v>
+        <v>79077</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-6</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5059,11 +5041,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>50080-AY0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5072,18 +5054,18 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5099,7 +5081,7 @@
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" s="1" t="n">
-        <v>46132</v>
+        <v>46150</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5110,18 +5092,18 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W49" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X49" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50">
@@ -5136,14 +5118,14 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="D50" t="n">
-        <v>79070</v>
+        <v>79148</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5153,11 +5135,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5166,11 +5148,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -5182,18 +5164,18 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" s="1" t="n">
-        <v>46132</v>
+        <v>46156</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5204,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -5212,10 +5194,10 @@
         </is>
       </c>
       <c r="W50" s="2" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="X50" t="n">
-        <v>4800</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="51">
@@ -5230,14 +5212,14 @@
         </is>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="D51" t="n">
-        <v>79071</v>
+        <v>79148</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>Y5-7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5247,11 +5229,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5260,11 +5242,11 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -5276,18 +5258,18 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" s="1" t="n">
-        <v>46132</v>
+        <v>46156</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5298,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -5306,32 +5288,32 @@
         </is>
       </c>
       <c r="W51" s="2" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="X51" t="n">
-        <v>3600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="D52" t="n">
-        <v>79071</v>
+        <v>79229</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>Y5-8</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5341,11 +5323,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30040-AG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5354,34 +5336,34 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30020-KG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" s="1" t="n">
-        <v>46132</v>
+        <v>46143</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5392,40 +5374,40 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="W52" s="2" t="n">
-        <v>46154</v>
+        <v>46143</v>
       </c>
       <c r="X52" t="n">
-        <v>5400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="D53" t="n">
-        <v>79072</v>
+        <v>79230</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>Y5-9</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5435,11 +5417,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2299</v>
+        <v>400</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5448,18 +5430,18 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>30020-KG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>2299</v>
+        <v>400</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5471,11 +5453,13 @@
         <v>46149</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+        <v>46157</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="R53" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5486,40 +5470,40 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2299</v>
+        <v>400</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W53" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X53" t="n">
-        <v>2400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="D54" t="n">
-        <v>79072</v>
+        <v>79230</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Y5-3</t>
+          <t>Y5-9</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5529,11 +5513,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-A   F</t>
+          <t>30040-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2299</v>
+        <v>400</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5542,18 +5526,18 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>30020-KG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>2299</v>
+        <v>400</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5565,11 +5549,13 @@
         <v>46149</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+        <v>46157</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="R54" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5580,675 +5566,17 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2299</v>
+        <v>400</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W54" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X54" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D55" t="n">
-        <v>79075</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Y5-4</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>200</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>200</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>接続,SEC</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" s="1" t="n">
-        <v>46153</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>200</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>熱融着機　湖南</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="X55" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>接続</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>熱融着機　湖南</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D56" t="n">
-        <v>79075</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Y5-4</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>50080-AY0B- 680X200F-AGA1F</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>200</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>200</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>接続,SEC</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>200</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>熱融着機　湖南</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="X56" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D57" t="n">
-        <v>79076</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Y5-5</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" s="1" t="n">
-        <v>46153</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1200</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
-      <c r="W57" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D58" t="n">
-        <v>79077</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Y5-6</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>スリット,SEC</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O58" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" s="1" t="n">
-        <v>46153</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
-      <c r="W58" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>スリット</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D59" t="n">
-        <v>79077</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Y5-6</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>50080-AY0B- 870X200F-A   C</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>スリット,SEC</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="O59" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SEC機　湖南</t>
-        </is>
-      </c>
-      <c r="W59" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="X59" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>スライス機1　湖南</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="D60" t="n">
-        <v>79148</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Y5-7</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="O60" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="P60" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>6000</v>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>スライス機1　湖南</t>
-        </is>
-      </c>
-      <c r="W60" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="X60" t="n">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>スライス機1　湖南</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="D61" t="n">
-        <v>79148</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Y5-7</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>スライス</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>6000</v>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>スライス機1　湖南</t>
-        </is>
-      </c>
-      <c r="W61" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="X61" t="n">
         <v>400</v>
       </c>
     </row>

--- a/code/結果_配台表.xlsx
+++ b/code/結果_配台表.xlsx
@@ -613,10 +613,8 @@
       <c r="H2" t="n">
         <v>300</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I2" t="n">
+        <v>6713</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -709,10 +707,8 @@
       <c r="H3" t="n">
         <v>1050</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I3" t="n">
+        <v>6713</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -764,7 +760,7 @@
         </is>
       </c>
       <c r="W3" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="X3" t="n">
         <v>1050</v>
@@ -805,10 +801,8 @@
       <c r="H4" t="n">
         <v>1050</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I4" t="n">
+        <v>6713</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -860,7 +854,7 @@
         </is>
       </c>
       <c r="W4" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="X4" t="n">
         <v>2100</v>
@@ -901,10 +895,8 @@
       <c r="H5" t="n">
         <v>300</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0   </t>
-        </is>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -995,10 +987,8 @@
       <c r="H6" t="n">
         <v>300</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0   </t>
-        </is>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1057,75 +1047,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="D7" t="n">
-        <v>78887</v>
+        <v>79141</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PN04-03</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X100   LG</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2300</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7C8 </t>
-        </is>
+        <v>8600</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6713</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FEL3002BY05WDLG-EC</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>梱包,EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>46140</v>
+        <v>46155</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1136,18 +1124,18 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="X7" t="n">
-        <v>2300</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="8">
@@ -1185,10 +1173,8 @@
       <c r="H8" t="n">
         <v>8600</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I8" t="n">
+        <v>6713</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1217,7 +1203,9 @@
       <c r="P8" s="1" t="n">
         <v>46157</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="R8" s="1" t="n">
         <v>46155</v>
       </c>
@@ -1238,32 +1226,32 @@
         </is>
       </c>
       <c r="W8" s="2" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="X8" t="n">
-        <v>5600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D9" t="n">
-        <v>79141</v>
+        <v>79142</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>V5-2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1277,27 +1265,25 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8600</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>2000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6713</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8600</v>
+        <v>2000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,7 +1297,9 @@
       <c r="P9" s="1" t="n">
         <v>46157</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="R9" s="1" t="n">
         <v>46155</v>
       </c>
@@ -1324,40 +1312,40 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>8600</v>
+        <v>2000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W9" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="X9" t="n">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D10" t="n">
-        <v>79141</v>
+        <v>79143</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>V5-3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1367,31 +1355,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30060-AG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8600</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6713</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1403,9 +1389,11 @@
         <v>46153</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>46156</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>46156</v>
+      </c>
       <c r="R10" s="1" t="n">
         <v>46155</v>
       </c>
@@ -1418,74 +1406,72 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W10" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46135</v>
+        <v>46120</v>
       </c>
       <c r="D11" t="n">
-        <v>79142</v>
+        <v>78624</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>V5-2</t>
+          <t>W4-12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>5700</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6783</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1494,14 +1480,16 @@
         </is>
       </c>
       <c r="O11" s="1" t="n">
-        <v>46153</v>
+        <v>46128</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>46142</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>46142</v>
+      </c>
       <c r="R11" s="1" t="n">
-        <v>46155</v>
+        <v>46141</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1509,93 +1497,93 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="U11" t="n">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W11" s="2" t="n">
-        <v>46154</v>
+        <v>46141</v>
       </c>
       <c r="X11" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="D12" t="n">
-        <v>79143</v>
+        <v>79067</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>V5-3</t>
+          <t>W5-1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-ABK0C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>300</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>1250</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6783</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>300</v>
+        <v>1250</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>46155</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="R12" s="1" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1606,40 +1594,40 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>300</v>
+        <v>1250</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="W12" s="2" t="n">
-        <v>46154</v>
+        <v>46143</v>
       </c>
       <c r="X12" t="n">
-        <v>300</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="D13" t="n">
-        <v>78624</v>
+        <v>79067</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>W4-12</t>
+          <t>W5-1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1649,49 +1637,47 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5700</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>1250</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6783</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>5700</v>
+        <v>1250</v>
       </c>
       <c r="L13" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
-        <v>46128</v>
+        <v>46143</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1699,10 +1685,10 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5700</v>
+        <v>1250</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1710,32 +1696,32 @@
         </is>
       </c>
       <c r="W13" s="2" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="X13" t="n">
-        <v>3300</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="D14" t="n">
-        <v>78624</v>
+        <v>79138</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>W4-12</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1749,12 +1735,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5700</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>6000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6783</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1762,10 +1746,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="L14" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1778,16 +1762,16 @@
         </is>
       </c>
       <c r="O14" s="1" t="n">
-        <v>46128</v>
+        <v>46153</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46142</v>
+        <v>46156</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46142</v>
+        <v>46160</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1795,10 +1779,10 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1806,126 +1790,126 @@
         </is>
       </c>
       <c r="W14" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="X14" t="n">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D15" t="n">
+        <v>79138</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1300X300F-A   P</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6783</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1300X300F-A   R</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>EC機　湖南</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79067</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>W5-1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>1250</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>EC,巻返し,欠点表示</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="P15" s="1" t="n">
+      <c r="W15" s="2" t="n">
         <v>46155</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1250</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>EC機　湖南</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>46143</v>
-      </c>
       <c r="X15" t="n">
-        <v>1250</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D16" t="n">
-        <v>79067</v>
+        <v>79138</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>W5-1</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1935,47 +1919,47 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>6000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6783</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>46156</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="R16" s="1" t="n">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1986,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1250</v>
+        <v>6000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1994,21 +1978,21 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="X16" t="n">
-        <v>1250</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
@@ -2035,10 +2019,8 @@
       <c r="H17" t="n">
         <v>6000</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I17" t="n">
+        <v>6783</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2067,9 +2049,11 @@
       <c r="P17" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="R17" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2088,10 +2072,10 @@
         </is>
       </c>
       <c r="W17" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="X17" t="n">
-        <v>4200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="18">
@@ -2109,11 +2093,11 @@
         <v>46135</v>
       </c>
       <c r="D18" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2129,10 +2113,8 @@
       <c r="H18" t="n">
         <v>6000</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I18" t="n">
+        <v>6783</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2159,9 +2141,11 @@
         <v>46153</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R18" s="1" t="n">
         <v>46155</v>
       </c>
@@ -2182,10 +2166,10 @@
         </is>
       </c>
       <c r="W18" s="2" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="X18" t="n">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="19">
@@ -2203,11 +2187,11 @@
         <v>46135</v>
       </c>
       <c r="D19" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2223,10 +2207,8 @@
       <c r="H19" t="n">
         <v>6000</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I19" t="n">
+        <v>6783</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2253,11 +2235,13 @@
         <v>46153</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R19" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2276,10 +2260,10 @@
         </is>
       </c>
       <c r="W19" s="2" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="X19" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20">
@@ -2297,11 +2281,11 @@
         <v>46135</v>
       </c>
       <c r="D20" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2317,10 +2301,8 @@
       <c r="H20" t="n">
         <v>6000</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I20" t="n">
+        <v>6783</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2347,11 +2329,13 @@
         <v>46153</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R20" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2370,7 +2354,7 @@
         </is>
       </c>
       <c r="W20" s="2" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="X20" t="n">
         <v>3300</v>
@@ -2391,11 +2375,11 @@
         <v>46135</v>
       </c>
       <c r="D21" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2411,10 +2395,8 @@
       <c r="H21" t="n">
         <v>6000</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I21" t="n">
+        <v>6783</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2441,11 +2423,13 @@
         <v>46153</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R21" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2464,10 +2448,10 @@
         </is>
       </c>
       <c r="W21" s="2" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="X21" t="n">
-        <v>2100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="22">
@@ -2485,11 +2469,11 @@
         <v>46135</v>
       </c>
       <c r="D22" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2499,24 +2483,22 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>9000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6783</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2532,14 +2514,16 @@
         </is>
       </c>
       <c r="O22" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>46154</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>46156</v>
+      </c>
       <c r="R22" s="1" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2550,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2558,10 +2542,10 @@
         </is>
       </c>
       <c r="W22" s="2" t="n">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="X22" t="n">
-        <v>2100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23">
@@ -2579,11 +2563,11 @@
         <v>46135</v>
       </c>
       <c r="D23" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2593,24 +2577,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>9000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6783</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2626,58 +2608,60 @@
         </is>
       </c>
       <c r="O23" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n">
         <v>46153</v>
       </c>
-      <c r="P23" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6000</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>EC機　湖南</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="n">
-        <v>46156</v>
-      </c>
       <c r="X23" t="n">
-        <v>3900</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="D24" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2687,24 +2671,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>9000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6783</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2720,14 +2702,16 @@
         </is>
       </c>
       <c r="O24" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>46154</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>46156</v>
+      </c>
       <c r="R24" s="1" t="n">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2738,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2746,10 +2730,10 @@
         </is>
       </c>
       <c r="W24" s="2" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="X24" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25">
@@ -2767,11 +2751,11 @@
         <v>46135</v>
       </c>
       <c r="D25" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2781,24 +2765,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>9000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6783</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2814,33 +2796,35 @@
         </is>
       </c>
       <c r="O25" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="n">
         <v>46153</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6000</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>EC機　湖南</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="n">
-        <v>46157</v>
       </c>
       <c r="X25" t="n">
         <v>3300</v>
@@ -2861,11 +2845,11 @@
         <v>46135</v>
       </c>
       <c r="D26" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-4</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2875,24 +2859,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>9000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6783</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2908,14 +2890,16 @@
         </is>
       </c>
       <c r="O26" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>46154</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>46156</v>
+      </c>
       <c r="R26" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2926,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2934,21 +2918,21 @@
         </is>
       </c>
       <c r="W26" s="2" t="n">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="X26" t="n">
-        <v>1500</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="C27" s="1" t="n">
@@ -2975,10 +2959,8 @@
       <c r="H27" t="n">
         <v>9000</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I27" t="n">
+        <v>6783</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3007,9 +2989,11 @@
       <c r="P27" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" s="1" t="n">
+        <v>46156</v>
+      </c>
       <c r="R27" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3028,82 +3012,82 @@
         </is>
       </c>
       <c r="W27" s="2" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="X27" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="D28" t="n">
-        <v>79140</v>
+        <v>79018</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y4-58</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>400</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6713</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>25020-AG00- 750X200F-AGR0C</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="P28" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="P28" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" s="1" t="n">
+        <v>46149</v>
+      </c>
       <c r="R28" s="1" t="n">
-        <v>46154</v>
+        <v>46143</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3114,90 +3098,90 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="X28" t="n">
-        <v>4800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="D29" t="n">
-        <v>79140</v>
+        <v>79019</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y4-59</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>7500</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6713</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="P29" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" s="1" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3208,90 +3192,90 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W29" s="2" t="n">
-        <v>46149</v>
+        <v>46143</v>
       </c>
       <c r="X29" t="n">
-        <v>1500</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="D30" t="n">
-        <v>79140</v>
+        <v>79019</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y4-59</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+        <v>7500</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6713</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="P30" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" s="1" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3302,63 +3286,61 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W30" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X30" t="n">
-        <v>3300</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="D31" t="n">
-        <v>79140</v>
+        <v>79070</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>9000</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I31" t="n">
+        <v>6713</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3369,7 +3351,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3383,9 +3365,11 @@
       <c r="P31" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R31" s="1" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3400,59 +3384,57 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W31" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="X31" t="n">
-        <v>3300</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="D32" t="n">
-        <v>79140</v>
+        <v>79070</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>W5-4</t>
+          <t>Y5-1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>9000</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
+      <c r="I32" t="n">
+        <v>6713</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3463,7 +3445,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3477,9 +3459,11 @@
       <c r="P32" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R32" s="1" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3494,36 +3478,36 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="X32" t="n">
-        <v>900</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="D33" t="n">
-        <v>79018</v>
+        <v>79232</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Y4-58</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3537,27 +3521,25 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>400</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>3600</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6713</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X200F-AGR0C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3566,14 +3548,16 @@
         </is>
       </c>
       <c r="O33" s="1" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R33" s="1" t="n">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3584,15 +3568,15 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="X33" t="n">
         <v>400</v>
@@ -3601,23 +3585,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="D34" t="n">
-        <v>79019</v>
+        <v>79232</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Y4-59</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3627,31 +3611,29 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>3600</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6713</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>7500</v>
+        <v>3600</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3660,14 +3642,16 @@
         </is>
       </c>
       <c r="O34" s="1" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R34" s="1" t="n">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3678,40 +3662,40 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>7500</v>
+        <v>3600</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="W34" s="2" t="n">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="X34" t="n">
-        <v>5100</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="D35" t="n">
-        <v>79019</v>
+        <v>79232</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Y4-59</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3721,31 +3705,29 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>3600</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6713</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>7500</v>
+        <v>3600</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3754,14 +3736,16 @@
         </is>
       </c>
       <c r="O35" s="1" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="R35" s="1" t="n">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3772,18 +3756,18 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>7500</v>
+        <v>3600</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="W35" s="2" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="X35" t="n">
-        <v>2400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36">
@@ -3798,14 +3782,14 @@
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="D36" t="n">
-        <v>79070</v>
+        <v>79286</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-11</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3821,10 +3805,8 @@
       <c r="H36" t="n">
         <v>9000</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I36" t="n">
+        <v>6713</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3844,18 +3826,18 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" s="1" t="n">
-        <v>46132</v>
+        <v>46157</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3874,10 +3856,10 @@
         </is>
       </c>
       <c r="W36" s="2" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="X36" t="n">
-        <v>3600</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="37">
@@ -3892,14 +3874,14 @@
         </is>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="D37" t="n">
-        <v>79070</v>
+        <v>79286</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-11</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3915,10 +3897,8 @@
       <c r="H37" t="n">
         <v>9000</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I37" t="n">
+        <v>6713</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3938,18 +3918,18 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" s="1" t="n">
-        <v>46132</v>
+        <v>46157</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3968,10 +3948,10 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="X37" t="n">
-        <v>600</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="38">
@@ -3986,14 +3966,14 @@
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="D38" t="n">
-        <v>79070</v>
+        <v>79287</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Y5-1</t>
+          <t>Y5-12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4009,10 +3989,8 @@
       <c r="H38" t="n">
         <v>9000</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I38" t="n">
+        <v>6713</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -4032,18 +4010,18 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" s="1" t="n">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4062,32 +4040,32 @@
         </is>
       </c>
       <c r="W38" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="X38" t="n">
-        <v>4800</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D39" t="n">
-        <v>79232</v>
+        <v>79287</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>Y5-12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4097,93 +4075,89 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H39" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6713</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>30020-BG00- 780X300F-A   V</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="X39" t="n">
         <v>3600</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>3600</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>分割,エンボス</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K </t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q39" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="R39" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3600</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>エンボス　湖南</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D40" t="n">
-        <v>79232</v>
+        <v>79288</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>Y5-13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4193,31 +4167,29 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>7500</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6713</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>3600</v>
+        <v>7500</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4226,16 +4198,14 @@
         </is>
       </c>
       <c r="O40" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q40" s="1" t="n">
-        <v>46162</v>
-      </c>
+        <v>46163</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" s="1" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4246,18 +4216,18 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3600</v>
+        <v>7500</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="W40" s="2" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="X40" t="n">
-        <v>2000</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="41">
@@ -4272,14 +4242,14 @@
         </is>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="D41" t="n">
-        <v>79071</v>
+        <v>79288</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Y5-2</t>
+          <t>Y5-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4293,12 +4263,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+        <v>7500</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6713</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4306,7 +4274,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4318,18 +4286,18 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4340,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4348,10 +4316,10 @@
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="X41" t="n">
-        <v>3600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="42">
@@ -4389,10 +4357,8 @@
       <c r="H42" t="n">
         <v>9000</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I42" t="n">
+        <v>6713</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -4421,9 +4387,11 @@
       <c r="P42" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="R42" s="1" t="n">
-        <v>46132</v>
+        <v>46154</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4442,10 +4410,10 @@
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="X42" t="n">
-        <v>5400</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="43">
@@ -4483,10 +4451,8 @@
       <c r="H43" t="n">
         <v>2299</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I43" t="n">
+        <v>6713</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4494,7 +4460,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2299</v>
+        <v>2200</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -4515,7 +4481,9 @@
       <c r="P43" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="R43" s="1" t="n">
         <v>46153</v>
       </c>
@@ -4528,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2299</v>
+        <v>2200</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4536,10 +4504,10 @@
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="X43" t="n">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="44">
@@ -4577,10 +4545,8 @@
       <c r="H44" t="n">
         <v>2299</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I44" t="n">
+        <v>6713</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -4588,7 +4554,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2299</v>
+        <v>2200</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4609,7 +4575,9 @@
       <c r="P44" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" s="1" t="n">
+        <v>46155</v>
+      </c>
       <c r="R44" s="1" t="n">
         <v>46150</v>
       </c>
@@ -4622,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2299</v>
+        <v>2200</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4630,10 +4598,10 @@
         </is>
       </c>
       <c r="W44" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="X44" t="n">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="45">
@@ -4671,10 +4639,8 @@
       <c r="H45" t="n">
         <v>200</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I45" t="n">
+        <v>6713</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -4703,7 +4669,9 @@
       <c r="P45" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R45" s="1" t="n">
         <v>46153</v>
       </c>
@@ -4724,7 +4692,7 @@
         </is>
       </c>
       <c r="W45" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="X45" t="n">
         <v>200</v>
@@ -4765,10 +4733,8 @@
       <c r="H46" t="n">
         <v>200</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I46" t="n">
+        <v>6713</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4797,7 +4763,9 @@
       <c r="P46" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R46" s="1" t="n">
         <v>46150</v>
       </c>
@@ -4818,7 +4786,7 @@
         </is>
       </c>
       <c r="W46" s="2" t="n">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="X46" t="n">
         <v>200</v>
@@ -4859,10 +4827,8 @@
       <c r="H47" t="n">
         <v>1200</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I47" t="n">
+        <v>6713</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4891,7 +4857,9 @@
       <c r="P47" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R47" s="1" t="n">
         <v>46153</v>
       </c>
@@ -4912,7 +4880,7 @@
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X47" t="n">
         <v>1200</v>
@@ -4953,10 +4921,8 @@
       <c r="H48" t="n">
         <v>2000</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I48" t="n">
+        <v>6713</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4985,7 +4951,9 @@
       <c r="P48" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R48" s="1" t="n">
         <v>46153</v>
       </c>
@@ -5006,7 +4974,7 @@
         </is>
       </c>
       <c r="W48" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="X48" t="n">
         <v>2000</v>
@@ -5047,10 +5015,8 @@
       <c r="H49" t="n">
         <v>2000</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I49" t="n">
+        <v>6713</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -5079,7 +5045,9 @@
       <c r="P49" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" s="1" t="n">
+        <v>46154</v>
+      </c>
       <c r="R49" s="1" t="n">
         <v>46150</v>
       </c>
@@ -5141,10 +5109,8 @@
       <c r="H50" t="n">
         <v>6000</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I50" t="n">
+        <v>6713</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -5173,7 +5139,9 @@
       <c r="P50" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="R50" s="1" t="n">
         <v>46156</v>
       </c>
@@ -5235,10 +5203,8 @@
       <c r="H51" t="n">
         <v>6000</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I51" t="n">
+        <v>6713</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -5267,7 +5233,9 @@
       <c r="P51" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="R51" s="1" t="n">
         <v>46156</v>
       </c>
@@ -5329,10 +5297,8 @@
       <c r="H52" t="n">
         <v>1600</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I52" t="n">
+        <v>6713</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5423,10 +5389,8 @@
       <c r="H53" t="n">
         <v>400</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I53" t="n">
+        <v>6713</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5519,10 +5483,8 @@
       <c r="H54" t="n">
         <v>400</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
+      <c r="I54" t="n">
+        <v>6713</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5555,7 +5517,7 @@
         <v>46157</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
